--- a/Experiments_frequency_bandpass_forgery.xlsx
+++ b/Experiments_frequency_bandpass_forgery.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UdS\Summer 2026\courses\TML\assignments\Assignment 4\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A964F8E-69C2-43BD-A2FA-8E9C3A541BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963346CC-6246-47DE-8023-17F2998FE961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
   <si>
     <t>Exp#</t>
   </si>
@@ -52,6 +52,12 @@
   </si>
   <si>
     <t>python approach_frequency_bandpass_forgery.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submissions/submission_freq_narrow --zip_out submission_freq_narrow.zip --strength 4 --low 0.10 --high 0.30</t>
+  </si>
+  <si>
+    <t>python approach_residual_fingerprint_forgery_perwm_adaptive_strength.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submissions/submission_adaptive --zip_out submission_adaptive.zip --strength 4 --sigmas 1.0,2.0,4.0 --aggregation median --adaptive_strength</t>
+  </si>
+  <si>
+    <t>residual_fingerprint_forgery_perwm_adaptive_strength</t>
   </si>
 </sst>
 </file>
@@ -399,7 +405,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
-    <col min="2" max="2" width="44.42578125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="52" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="107.5703125" style="1" customWidth="1"/>
     <col min="4" max="4" width="16" style="3" customWidth="1"/>
   </cols>
@@ -442,6 +448,9 @@
       <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
@@ -453,9 +462,23 @@
       <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="D4" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C5" s="3"/>
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C6" s="3"/>

--- a/Experiments_frequency_bandpass_forgery.xlsx
+++ b/Experiments_frequency_bandpass_forgery.xlsx
@@ -8,24 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UdS\Summer 2026\courses\TML\assignments\Assignment 4\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963346CC-6246-47DE-8023-17F2998FE961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A699B797-D10F-439D-BF8C-0A5188A4C3F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
   <si>
     <t>Exp#</t>
   </si>
@@ -58,6 +67,33 @@
   </si>
   <si>
     <t>residual_fingerprint_forgery_perwm_adaptive_strength</t>
+  </si>
+  <si>
+    <t>python approach_residual_fingerprint_consensus.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submission_consensus --zip_out submission_consensus.zip --strength 4 --sigmas 4.0 --aggregation median</t>
+  </si>
+  <si>
+    <t>approach_residual_fingerprint_consensus</t>
+  </si>
+  <si>
+    <t>per class wm</t>
+  </si>
+  <si>
+    <t>GROUP_CONFIGS: dict[str, GroupConfig] = {
+    # Low-freq spread-spectrum: large sigmas to capture low-frequency watermark signal
+    "WM_1": GroupConfig(strategy="residual", strength=6.0, sigmas=[8.0, 16.0, 32.0]),
+    "WM_2": GroupConfig(strategy="residual", strength=6.0, sigmas=[8.0, 16.0, 32.0]),
+    "WM_3": GroupConfig(strategy="residual", strength=6.0, sigmas=[8.0, 16.0, 32.0]),
+    "WM_8": GroupConfig(strategy="residual", strength=6.0, sigmas=[8.0, 16.0, 32.0]),
+    # DWT subband: bandpass targeting subband frequency boundaries
+    "WM_4": GroupConfig(strategy="bandpass", strength=8.0, freq_low=0.10, freq_high=0.25),
+    # Spatial template / mid-frequency
+    "WM_5": GroupConfig(strategy="residual", strength=7.0, sigmas=[4.0, 8.0]),
+    # Tiled/periodic spatial: low-frequency bandpass
+    "WM_6": GroupConfig(strategy="bandpass", strength=6.0, freq_low=0.01, freq_high=0.15),
+    # Vertical stripe: directional vertical-only FFT mask
+    "WM_7": GroupConfig(strategy="vertical", strength=6.0, vert_low=0.06, vert_high=0.40,
+                        vert_horiz_suppress=0.04),
+}</t>
   </si>
 </sst>
 </file>
@@ -481,10 +517,32 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C6" s="3"/>
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C7" s="3"/>
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C8" s="3"/>
